--- a/uploads/invalid_yassine el  jabri.xlsx
+++ b/uploads/invalid_yassine el  jabri.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>TEL CLIENT</t>
   </si>
@@ -32,6 +32,15 @@
   </si>
   <si>
     <t>0661250473</t>
+  </si>
+  <si>
+    <t>0611111111</t>
+  </si>
+  <si>
+    <t>18924.38a</t>
+  </si>
+  <si>
+    <t>999.12s</t>
   </si>
 </sst>
 </file>
@@ -389,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -432,8 +441,8 @@
       <c r="B4">
         <v>3174265</v>
       </c>
-      <c r="C4">
-        <v>18924.38</v>
+      <c r="C4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -445,6 +454,17 @@
       </c>
       <c r="C5">
         <v>16666.51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>999</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
